--- a/docs/API_명세서.xlsx
+++ b/docs/API_명세서.xlsx
@@ -1076,7 +1076,7 @@
       </c>
       <c r="S5" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="S6" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="S7" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="S8" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="S9" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="S10" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="S11" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="S12" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="S13" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="S14" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="S15" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="S16" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="S17" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="S18" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="S19" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S20" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="S21" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="S22" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="S23" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="S24" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="S25" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="S26" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="S27" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="S28" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="S29" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="S30" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="S31" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="S32" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="S33" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="S34" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="S35" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="S36" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="S37" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="S38" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="S39" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="S40" s="61" t="inlineStr">
         <is>
-          <t>대기중</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="T40" s="41" t="n"/>
@@ -25927,8 +25927,8 @@
     <mergeCell ref="M3:P3"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A3:A4"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:R4"/>

--- a/docs/API_명세서.xlsx
+++ b/docs/API_명세서.xlsx
@@ -802,18 +802,25 @@
       <c r="D2" s="51" t="n"/>
       <c r="Q2" s="52" t="inlineStr">
         <is>
-          <t>400 VALIDATION_ERROR: 필수 필드 누락/형식 오류
-401 AUTH_INVALID_TOKEN: 토큰 누락/만료
+          <t>401 AUTH_INVALID_CREDENTIALS: 이메일 또는 비밀번호 불일치
+400 VALIDATION_ERROR: 필수 필드 누락/형식 오류
+400 FILE_INVALID_TYPE: 허용되지 않는 파일 확장자
+401 AUTH_INVALID_TOKEN: 토큰 누락/유효하지 않음
+401 AUTH_TOKEN_EXPIRED: 토큰 만료
 403 AUTH_FORBIDDEN: 권한 없는 리소스 접근
 404 RESOURCE_NOT_FOUND: 대상 리소스 없음
 409 STATE_CONFLICT: 처리 상태 미충족
+409 DUPLICATE_EMAIL: 이메일 중복
+409 DUPLICATE_PHONE: 휴대폰 번호 중복
 413 FILE_TOO_LARGE: 파일 크기 제한 초과
+422 VALIDATION_ERROR: 입력값 검증 실패(RequestValidationError)
 422 OCR_LOW_CONFIDENCE: OCR 신뢰도 임계값 미달
+423 AUTH_ACCOUNT_INACTIVE: 비활성화 계정 접근
 429 RATE_LIMITED: 요청 과다
 500 INTERNAL_ERROR: 서버 내부 오류
-502 UPSTREAM_OCR_ERROR: 외부 OCR API 실패
-503 QUEUE_UNAVAILABLE: 비동기 큐 등록 실패
-504 UPSTREAM_TIMEOUT: 외부 LLM/OCR 타임아웃</t>
+503 OCR_QUEUE_UNAVAILABLE: OCR 비동기 작업 큐 등록 실패
+503 QUEUE_UNAVAILABLE: 비동기 작업 큐 등록 실패(서비스 일시 불가)
+504 EXTERNAL_SERVICE_TIMEOUT: 외부 LLM/OCR 타임아웃</t>
         </is>
       </c>
       <c r="S2" s="53" t="n"/>
@@ -1215,7 +1222,7 @@
       </c>
       <c r="C7" s="61" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D7" s="61" t="inlineStr">
@@ -1690,7 +1697,7 @@
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>api/v1/profiles/health</t>
+          <t>api/v1/users/me/health-profile</t>
         </is>
       </c>
       <c r="C11" s="37" t="inlineStr">
@@ -1834,7 +1841,7 @@
       </c>
       <c r="B12" s="62" t="inlineStr">
         <is>
-          <t>api/v1/profiles/health</t>
+          <t>api/v1/users/me/health-profile</t>
         </is>
       </c>
       <c r="C12" s="61" t="inlineStr">
@@ -5670,25 +5677,61 @@
       <c r="AB40" s="41" t="n"/>
     </row>
     <row r="41" ht="168" customHeight="1" s="47">
-      <c r="A41" s="42" t="n"/>
-      <c r="B41" s="43" t="n"/>
-      <c r="C41" s="42" t="n"/>
-      <c r="D41" s="42" t="n"/>
-      <c r="E41" s="44" t="n"/>
-      <c r="F41" s="44" t="n"/>
-      <c r="G41" s="43" t="n"/>
-      <c r="H41" s="43" t="n"/>
-      <c r="I41" s="44" t="n"/>
-      <c r="J41" s="44" t="n"/>
-      <c r="K41" s="43" t="n"/>
-      <c r="L41" s="43" t="n"/>
-      <c r="M41" s="43" t="n"/>
-      <c r="N41" s="43" t="n"/>
-      <c r="O41" s="43" t="n"/>
-      <c r="P41" s="43" t="n"/>
-      <c r="Q41" s="43" t="n"/>
-      <c r="R41" s="44" t="n"/>
-      <c r="S41" s="42" t="n"/>
+      <c r="A41" s="61" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B41" s="62" t="inlineStr">
+        <is>
+          <t>api/v1/auth/logout</t>
+        </is>
+      </c>
+      <c r="C41" s="61" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D41" s="61" t="inlineStr">
+        <is>
+          <t>로그아웃</t>
+        </is>
+      </c>
+      <c r="E41" s="40" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;access_token&gt; (필수)</t>
+        </is>
+      </c>
+      <c r="F41" s="40" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;access_token&gt; eyJhbGciOi...</t>
+        </is>
+      </c>
+      <c r="G41" s="64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" s="64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" s="39" t="n"/>
+      <c r="J41" s="39" t="n"/>
+      <c r="K41" s="64" t="n"/>
+      <c r="L41" s="64" t="n"/>
+      <c r="M41" s="65" t="n"/>
+      <c r="N41" s="65" t="n"/>
+      <c r="O41" s="65" t="n"/>
+      <c r="P41" s="65" t="n"/>
+      <c r="Q41" s="62" t="n"/>
+      <c r="R41" s="27" t="n"/>
+      <c r="S41" s="61" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="T41" s="45" t="n"/>
       <c r="U41" s="45" t="n"/>
       <c r="V41" s="45" t="n"/>
@@ -5700,130 +5743,346 @@
       <c r="AB41" s="45" t="n"/>
     </row>
     <row r="42" ht="168" customHeight="1" s="47">
-      <c r="A42" s="46" t="n"/>
-      <c r="B42" s="46" t="n"/>
-      <c r="C42" s="46" t="n"/>
-      <c r="D42" s="46" t="n"/>
-      <c r="E42" s="46" t="n"/>
-      <c r="F42" s="46" t="n"/>
-      <c r="G42" s="46" t="n"/>
-      <c r="H42" s="46" t="n"/>
-      <c r="I42" s="46" t="n"/>
-      <c r="J42" s="46" t="n"/>
-      <c r="K42" s="46" t="n"/>
-      <c r="L42" s="46" t="n"/>
-      <c r="M42" s="46" t="n"/>
-      <c r="N42" s="46" t="n"/>
-      <c r="O42" s="46" t="n"/>
-      <c r="P42" s="46" t="n"/>
-      <c r="Q42" s="46" t="n"/>
-      <c r="R42" s="46" t="n"/>
-      <c r="S42" s="46" t="n"/>
+      <c r="A42" s="61" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B42" s="62" t="inlineStr">
+        <is>
+          <t>api/v1/medications/info</t>
+        </is>
+      </c>
+      <c r="C42" s="61" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D42" s="61" t="inlineStr">
+        <is>
+          <t>약물 상세 정보 조회</t>
+        </is>
+      </c>
+      <c r="E42" s="40" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;access_token&gt; (필수)</t>
+        </is>
+      </c>
+      <c r="F42" s="40" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;access_token&gt; eyJhbGciOi...</t>
+        </is>
+      </c>
+      <c r="G42" s="64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" s="64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="39" t="n"/>
+      <c r="J42" s="39" t="n"/>
+      <c r="K42" s="64" t="n"/>
+      <c r="L42" s="64" t="n"/>
+      <c r="M42" s="65" t="n"/>
+      <c r="N42" s="65" t="n"/>
+      <c r="O42" s="65" t="n"/>
+      <c r="P42" s="65" t="n"/>
+      <c r="Q42" s="62" t="n"/>
+      <c r="R42" s="27" t="n"/>
+      <c r="S42" s="61" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="84" customHeight="1" s="47">
-      <c r="A43" s="46" t="n"/>
-      <c r="B43" s="46" t="n"/>
-      <c r="C43" s="46" t="n"/>
-      <c r="D43" s="46" t="n"/>
-      <c r="E43" s="46" t="n"/>
-      <c r="F43" s="46" t="n"/>
-      <c r="G43" s="46" t="n"/>
-      <c r="H43" s="46" t="n"/>
-      <c r="I43" s="46" t="n"/>
-      <c r="J43" s="46" t="n"/>
-      <c r="K43" s="46" t="n"/>
-      <c r="L43" s="46" t="n"/>
-      <c r="M43" s="46" t="n"/>
-      <c r="N43" s="46" t="n"/>
-      <c r="O43" s="46" t="n"/>
-      <c r="P43" s="46" t="n"/>
-      <c r="Q43" s="46" t="n"/>
-      <c r="R43" s="46" t="n"/>
-      <c r="S43" s="46" t="n"/>
+      <c r="A43" s="61" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B43" s="62" t="inlineStr">
+        <is>
+          <t>api/v1/guides/jobs/confirm-and-create</t>
+        </is>
+      </c>
+      <c r="C43" s="61" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D43" s="61" t="inlineStr">
+        <is>
+          <t>OCR 확정+가이드 생성</t>
+        </is>
+      </c>
+      <c r="E43" s="40" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;access_token&gt; (필수)</t>
+        </is>
+      </c>
+      <c r="F43" s="40" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;access_token&gt; eyJhbGciOi...</t>
+        </is>
+      </c>
+      <c r="G43" s="64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="39" t="n"/>
+      <c r="J43" s="39" t="n"/>
+      <c r="K43" s="64" t="n"/>
+      <c r="L43" s="64" t="n"/>
+      <c r="M43" s="65" t="n"/>
+      <c r="N43" s="65" t="n"/>
+      <c r="O43" s="65" t="n"/>
+      <c r="P43" s="65" t="n"/>
+      <c r="Q43" s="62" t="n"/>
+      <c r="R43" s="27" t="n"/>
+      <c r="S43" s="61" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="47">
-      <c r="A44" s="46" t="n"/>
-      <c r="B44" s="46" t="n"/>
-      <c r="C44" s="46" t="n"/>
-      <c r="D44" s="46" t="n"/>
-      <c r="E44" s="46" t="n"/>
-      <c r="F44" s="46" t="n"/>
-      <c r="G44" s="46" t="n"/>
-      <c r="H44" s="46" t="n"/>
-      <c r="I44" s="46" t="n"/>
-      <c r="J44" s="46" t="n"/>
-      <c r="K44" s="46" t="n"/>
-      <c r="L44" s="46" t="n"/>
-      <c r="M44" s="46" t="n"/>
-      <c r="N44" s="46" t="n"/>
-      <c r="O44" s="46" t="n"/>
-      <c r="P44" s="46" t="n"/>
-      <c r="Q44" s="46" t="n"/>
-      <c r="R44" s="46" t="n"/>
-      <c r="S44" s="46" t="n"/>
+      <c r="A44" s="61" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B44" s="62" t="inlineStr">
+        <is>
+          <t>api/v1/notifications/read</t>
+        </is>
+      </c>
+      <c r="C44" s="61" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D44" s="61" t="inlineStr">
+        <is>
+          <t>읽은 알림 삭제</t>
+        </is>
+      </c>
+      <c r="E44" s="40" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;access_token&gt; (필수)</t>
+        </is>
+      </c>
+      <c r="F44" s="40" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;access_token&gt; eyJhbGciOi...</t>
+        </is>
+      </c>
+      <c r="G44" s="64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" s="64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="39" t="n"/>
+      <c r="J44" s="39" t="n"/>
+      <c r="K44" s="64" t="n"/>
+      <c r="L44" s="64" t="n"/>
+      <c r="M44" s="65" t="n"/>
+      <c r="N44" s="65" t="n"/>
+      <c r="O44" s="65" t="n"/>
+      <c r="P44" s="65" t="n"/>
+      <c r="Q44" s="62" t="n"/>
+      <c r="R44" s="27" t="n"/>
+      <c r="S44" s="61" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="47">
-      <c r="A45" s="46" t="n"/>
-      <c r="B45" s="46" t="n"/>
-      <c r="C45" s="46" t="n"/>
-      <c r="D45" s="46" t="n"/>
-      <c r="E45" s="46" t="n"/>
-      <c r="F45" s="46" t="n"/>
-      <c r="G45" s="46" t="n"/>
-      <c r="H45" s="46" t="n"/>
-      <c r="I45" s="46" t="n"/>
-      <c r="J45" s="46" t="n"/>
-      <c r="K45" s="46" t="n"/>
-      <c r="L45" s="46" t="n"/>
-      <c r="M45" s="46" t="n"/>
-      <c r="N45" s="46" t="n"/>
-      <c r="O45" s="46" t="n"/>
-      <c r="P45" s="46" t="n"/>
-      <c r="Q45" s="46" t="n"/>
-      <c r="R45" s="46" t="n"/>
-      <c r="S45" s="46" t="n"/>
+      <c r="A45" s="61" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B45" s="62" t="inlineStr">
+        <is>
+          <t>api/v1/notifications/settings</t>
+        </is>
+      </c>
+      <c r="C45" s="61" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D45" s="61" t="inlineStr">
+        <is>
+          <t>알림 설정 조회</t>
+        </is>
+      </c>
+      <c r="E45" s="40" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;access_token&gt; (필수)</t>
+        </is>
+      </c>
+      <c r="F45" s="40" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;access_token&gt; eyJhbGciOi...</t>
+        </is>
+      </c>
+      <c r="G45" s="64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" s="64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="39" t="n"/>
+      <c r="J45" s="39" t="n"/>
+      <c r="K45" s="64" t="n"/>
+      <c r="L45" s="64" t="n"/>
+      <c r="M45" s="65" t="n"/>
+      <c r="N45" s="65" t="n"/>
+      <c r="O45" s="65" t="n"/>
+      <c r="P45" s="65" t="n"/>
+      <c r="Q45" s="62" t="n"/>
+      <c r="R45" s="27" t="n"/>
+      <c r="S45" s="61" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="47">
-      <c r="A46" s="46" t="n"/>
-      <c r="B46" s="46" t="n"/>
-      <c r="C46" s="46" t="n"/>
-      <c r="D46" s="46" t="n"/>
-      <c r="E46" s="46" t="n"/>
-      <c r="F46" s="46" t="n"/>
-      <c r="G46" s="46" t="n"/>
-      <c r="H46" s="46" t="n"/>
-      <c r="I46" s="46" t="n"/>
-      <c r="J46" s="46" t="n"/>
-      <c r="K46" s="46" t="n"/>
-      <c r="L46" s="46" t="n"/>
-      <c r="M46" s="46" t="n"/>
-      <c r="N46" s="46" t="n"/>
-      <c r="O46" s="46" t="n"/>
-      <c r="P46" s="46" t="n"/>
-      <c r="Q46" s="46" t="n"/>
-      <c r="R46" s="46" t="n"/>
-      <c r="S46" s="46" t="n"/>
+      <c r="A46" s="61" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B46" s="62" t="inlineStr">
+        <is>
+          <t>api/v1/notifications/settings</t>
+        </is>
+      </c>
+      <c r="C46" s="61" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D46" s="61" t="inlineStr">
+        <is>
+          <t>알림 설정 수정</t>
+        </is>
+      </c>
+      <c r="E46" s="40" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;access_token&gt; (필수)</t>
+        </is>
+      </c>
+      <c r="F46" s="40" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;access_token&gt; eyJhbGciOi...</t>
+        </is>
+      </c>
+      <c r="G46" s="64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" s="64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="39" t="n"/>
+      <c r="J46" s="39" t="n"/>
+      <c r="K46" s="64" t="n"/>
+      <c r="L46" s="64" t="n"/>
+      <c r="M46" s="65" t="n"/>
+      <c r="N46" s="65" t="n"/>
+      <c r="O46" s="65" t="n"/>
+      <c r="P46" s="65" t="n"/>
+      <c r="Q46" s="62" t="n"/>
+      <c r="R46" s="27" t="n"/>
+      <c r="S46" s="61" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="47">
-      <c r="A47" s="46" t="n"/>
-      <c r="B47" s="46" t="n"/>
-      <c r="C47" s="46" t="n"/>
-      <c r="D47" s="46" t="n"/>
-      <c r="E47" s="46" t="n"/>
-      <c r="F47" s="46" t="n"/>
-      <c r="G47" s="46" t="n"/>
-      <c r="H47" s="46" t="n"/>
-      <c r="I47" s="46" t="n"/>
-      <c r="J47" s="46" t="n"/>
-      <c r="K47" s="46" t="n"/>
-      <c r="L47" s="46" t="n"/>
-      <c r="M47" s="46" t="n"/>
-      <c r="N47" s="46" t="n"/>
-      <c r="O47" s="46" t="n"/>
-      <c r="P47" s="46" t="n"/>
-      <c r="Q47" s="46" t="n"/>
-      <c r="R47" s="46" t="n"/>
-      <c r="S47" s="46" t="n"/>
+      <c r="A47" s="61" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B47" s="62" t="inlineStr">
+        <is>
+          <t>api/v1/drugs</t>
+        </is>
+      </c>
+      <c r="C47" s="61" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D47" s="61" t="inlineStr">
+        <is>
+          <t>ADHD 약물 DB 검색</t>
+        </is>
+      </c>
+      <c r="E47" s="40" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;access_token&gt; (필수)</t>
+        </is>
+      </c>
+      <c r="F47" s="40" t="inlineStr">
+        <is>
+          <t>Authorization: Bearer &lt;access_token&gt; eyJhbGciOi...</t>
+        </is>
+      </c>
+      <c r="G47" s="64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" s="64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="39" t="n"/>
+      <c r="J47" s="39" t="n"/>
+      <c r="K47" s="64" t="n"/>
+      <c r="L47" s="64" t="n"/>
+      <c r="M47" s="65" t="n"/>
+      <c r="N47" s="65" t="n"/>
+      <c r="O47" s="65" t="n"/>
+      <c r="P47" s="65" t="n"/>
+      <c r="Q47" s="62" t="n"/>
+      <c r="R47" s="27" t="n"/>
+      <c r="S47" s="61" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="47">
       <c r="A48" s="46" t="n"/>

--- a/docs/API_명세서.xlsx
+++ b/docs/API_명세서.xlsx
@@ -1078,7 +1078,7 @@
       </c>
       <c r="R5" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S5" s="61" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="R6" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S6" s="61" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="R7" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S7" s="61" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="R8" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S8" s="61" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="R9" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S9" s="61" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R10" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S10" s="61" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R11" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S11" s="61" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R12" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S12" s="61" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="R13" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S13" s="61" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="R14" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S14" s="61" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="R15" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S15" s="61" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="R16" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S16" s="61" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="R17" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S17" s="61" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="R18" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S18" s="61" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="R19" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S19" s="61" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R20" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S20" s="61" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="R21" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S21" s="61" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="R22" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S22" s="61" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="R23" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S23" s="61" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="R24" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S24" s="61" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="R25" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S25" s="61" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="R26" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S26" s="61" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R27" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S27" s="61" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="R28" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S28" s="61" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="R29" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S29" s="61" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="R30" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S30" s="61" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="R31" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S31" s="61" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="R32" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S32" s="61" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="R33" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S33" s="61" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="R34" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S34" s="61" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="R35" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S35" s="61" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="R36" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S36" s="61" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="R37" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S37" s="61" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="R38" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S38" s="61" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="R39" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S39" s="61" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="R40" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S40" s="61" t="inlineStr">
@@ -5726,7 +5726,11 @@
       <c r="O41" s="65" t="n"/>
       <c r="P41" s="65" t="n"/>
       <c r="Q41" s="62" t="n"/>
-      <c r="R41" s="27" t="n"/>
+      <c r="R41" s="27" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S41" s="61" t="inlineStr">
         <is>
           <t>개발완료</t>
@@ -5792,7 +5796,11 @@
       <c r="O42" s="65" t="n"/>
       <c r="P42" s="65" t="n"/>
       <c r="Q42" s="62" t="n"/>
-      <c r="R42" s="27" t="n"/>
+      <c r="R42" s="27" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S42" s="61" t="inlineStr">
         <is>
           <t>개발완료</t>
@@ -5849,7 +5857,11 @@
       <c r="O43" s="65" t="n"/>
       <c r="P43" s="65" t="n"/>
       <c r="Q43" s="62" t="n"/>
-      <c r="R43" s="27" t="n"/>
+      <c r="R43" s="27" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S43" s="61" t="inlineStr">
         <is>
           <t>개발완료</t>
@@ -5906,7 +5918,11 @@
       <c r="O44" s="65" t="n"/>
       <c r="P44" s="65" t="n"/>
       <c r="Q44" s="62" t="n"/>
-      <c r="R44" s="27" t="n"/>
+      <c r="R44" s="27" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S44" s="61" t="inlineStr">
         <is>
           <t>개발완료</t>
@@ -5963,7 +5979,11 @@
       <c r="O45" s="65" t="n"/>
       <c r="P45" s="65" t="n"/>
       <c r="Q45" s="62" t="n"/>
-      <c r="R45" s="27" t="n"/>
+      <c r="R45" s="27" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S45" s="61" t="inlineStr">
         <is>
           <t>개발완료</t>
@@ -6020,7 +6040,11 @@
       <c r="O46" s="65" t="n"/>
       <c r="P46" s="65" t="n"/>
       <c r="Q46" s="62" t="n"/>
-      <c r="R46" s="27" t="n"/>
+      <c r="R46" s="27" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S46" s="61" t="inlineStr">
         <is>
           <t>개발완료</t>
@@ -6077,7 +6101,11 @@
       <c r="O47" s="65" t="n"/>
       <c r="P47" s="65" t="n"/>
       <c r="Q47" s="62" t="n"/>
-      <c r="R47" s="27" t="n"/>
+      <c r="R47" s="27" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S47" s="61" t="inlineStr">
         <is>
           <t>개발완료</t>
@@ -6085,10 +6113,26 @@
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="47">
-      <c r="A48" s="46" t="n"/>
-      <c r="B48" s="46" t="n"/>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
+      <c r="A48" s="46" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B48" s="46" t="inlineStr">
+        <is>
+          <t>api/v1/guides/jobs/latest</t>
+        </is>
+      </c>
+      <c r="C48" s="46" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D48" s="46" t="inlineStr">
+        <is>
+          <t>가이드 최신 작업 상태 조회</t>
+        </is>
+      </c>
       <c r="E48" s="46" t="n"/>
       <c r="F48" s="46" t="n"/>
       <c r="G48" s="46" t="n"/>
@@ -6102,14 +6146,34 @@
       <c r="O48" s="46" t="n"/>
       <c r="P48" s="46" t="n"/>
       <c r="Q48" s="46" t="n"/>
-      <c r="R48" s="46" t="n"/>
+      <c r="R48" s="46" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S48" s="46" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="47">
-      <c r="A49" s="46" t="n"/>
-      <c r="B49" s="46" t="n"/>
-      <c r="C49" s="46" t="n"/>
-      <c r="D49" s="46" t="n"/>
+      <c r="A49" s="46" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B49" s="46" t="inlineStr">
+        <is>
+          <t>api/v1/guides/jobs/{job_id}/feedback</t>
+        </is>
+      </c>
+      <c r="C49" s="46" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D49" s="46" t="inlineStr">
+        <is>
+          <t>가이드 피드백 제출</t>
+        </is>
+      </c>
       <c r="E49" s="46" t="n"/>
       <c r="F49" s="46" t="n"/>
       <c r="G49" s="46" t="n"/>
@@ -6123,14 +6187,34 @@
       <c r="O49" s="46" t="n"/>
       <c r="P49" s="46" t="n"/>
       <c r="Q49" s="46" t="n"/>
-      <c r="R49" s="46" t="n"/>
+      <c r="R49" s="46" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S49" s="46" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="47">
-      <c r="A50" s="46" t="n"/>
-      <c r="B50" s="46" t="n"/>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
+      <c r="A50" s="46" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B50" s="46" t="inlineStr">
+        <is>
+          <t>api/v1/guides/feedback/summary</t>
+        </is>
+      </c>
+      <c r="C50" s="46" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D50" s="46" t="inlineStr">
+        <is>
+          <t>가이드 피드백 통계 조회</t>
+        </is>
+      </c>
       <c r="E50" s="46" t="n"/>
       <c r="F50" s="46" t="n"/>
       <c r="G50" s="46" t="n"/>
@@ -6144,14 +6228,34 @@
       <c r="O50" s="46" t="n"/>
       <c r="P50" s="46" t="n"/>
       <c r="Q50" s="46" t="n"/>
-      <c r="R50" s="46" t="n"/>
+      <c r="R50" s="46" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S50" s="46" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="47">
-      <c r="A51" s="46" t="n"/>
-      <c r="B51" s="46" t="n"/>
-      <c r="C51" s="46" t="n"/>
-      <c r="D51" s="46" t="n"/>
+      <c r="A51" s="46" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B51" s="46" t="inlineStr">
+        <is>
+          <t>api/v1/ocr/jobs/{job_id}/result/confirm</t>
+        </is>
+      </c>
+      <c r="C51" s="46" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D51" s="46" t="inlineStr">
+        <is>
+          <t>OCR 결과 확정 저장</t>
+        </is>
+      </c>
       <c r="E51" s="46" t="n"/>
       <c r="F51" s="46" t="n"/>
       <c r="G51" s="46" t="n"/>
@@ -6165,14 +6269,34 @@
       <c r="O51" s="46" t="n"/>
       <c r="P51" s="46" t="n"/>
       <c r="Q51" s="46" t="n"/>
-      <c r="R51" s="46" t="n"/>
+      <c r="R51" s="46" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S51" s="46" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="47">
-      <c r="A52" s="46" t="n"/>
-      <c r="B52" s="46" t="n"/>
-      <c r="C52" s="46" t="n"/>
-      <c r="D52" s="46" t="n"/>
+      <c r="A52" s="46" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B52" s="46" t="inlineStr">
+        <is>
+          <t>api/v1/diaries/{diary_date}</t>
+        </is>
+      </c>
+      <c r="C52" s="46" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D52" s="46" t="inlineStr">
+        <is>
+          <t>일기 저장/갱신(upsert)</t>
+        </is>
+      </c>
       <c r="E52" s="46" t="n"/>
       <c r="F52" s="46" t="n"/>
       <c r="G52" s="46" t="n"/>
@@ -6186,14 +6310,34 @@
       <c r="O52" s="46" t="n"/>
       <c r="P52" s="46" t="n"/>
       <c r="Q52" s="46" t="n"/>
-      <c r="R52" s="46" t="n"/>
+      <c r="R52" s="46" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S52" s="46" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="47">
-      <c r="A53" s="46" t="n"/>
-      <c r="B53" s="46" t="n"/>
-      <c r="C53" s="46" t="n"/>
-      <c r="D53" s="46" t="n"/>
+      <c r="A53" s="46" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B53" s="46" t="inlineStr">
+        <is>
+          <t>api/v1/diaries/{diary_date}</t>
+        </is>
+      </c>
+      <c r="C53" s="46" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D53" s="46" t="inlineStr">
+        <is>
+          <t>일기 단건 조회</t>
+        </is>
+      </c>
       <c r="E53" s="46" t="n"/>
       <c r="F53" s="46" t="n"/>
       <c r="G53" s="46" t="n"/>
@@ -6207,14 +6351,34 @@
       <c r="O53" s="46" t="n"/>
       <c r="P53" s="46" t="n"/>
       <c r="Q53" s="46" t="n"/>
-      <c r="R53" s="46" t="n"/>
+      <c r="R53" s="46" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S53" s="46" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="47">
-      <c r="A54" s="46" t="n"/>
-      <c r="B54" s="46" t="n"/>
-      <c r="C54" s="46" t="n"/>
-      <c r="D54" s="46" t="n"/>
+      <c r="A54" s="46" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B54" s="46" t="inlineStr">
+        <is>
+          <t>api/v1/diaries</t>
+        </is>
+      </c>
+      <c r="C54" s="46" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D54" s="46" t="inlineStr">
+        <is>
+          <t>일기 목록 조회(기간)</t>
+        </is>
+      </c>
       <c r="E54" s="46" t="n"/>
       <c r="F54" s="46" t="n"/>
       <c r="G54" s="46" t="n"/>
@@ -6228,7 +6392,11 @@
       <c r="O54" s="46" t="n"/>
       <c r="P54" s="46" t="n"/>
       <c r="Q54" s="46" t="n"/>
-      <c r="R54" s="46" t="n"/>
+      <c r="R54" s="46" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S54" s="46" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="47">
@@ -26186,8 +26354,8 @@
     <mergeCell ref="M3:P3"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:R4"/>
